--- a/data/trans_camb/PCS12_SP_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,89</t>
+          <t>-3,12; 5,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,68</t>
+          <t>-2,85; 6,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,16</t>
+          <t>-2,59; 5,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 3,34</t>
+          <t>-9,3; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 2,9</t>
+          <t>-8,54; 3,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 6,97</t>
+          <t>-4,03; 6,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,46</t>
+          <t>-4,06; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,93</t>
+          <t>-3,5; 3,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,31</t>
+          <t>-1,04; 5,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 58,52</t>
+          <t>-22,17; 57,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 66,89</t>
+          <t>-20,79; 62,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 62,79</t>
+          <t>-17,9; 59,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 22,22</t>
+          <t>-42,78; 22,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,48; 20,4</t>
+          <t>-41,14; 24,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 46,97</t>
+          <t>-18,28; 46,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 29,77</t>
+          <t>-24,73; 25,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 30,56</t>
+          <t>-21,91; 29,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 43,46</t>
+          <t>-6,32; 45,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,99</t>
+          <t>1,17; 11,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,64</t>
+          <t>-2,29; 6,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,25</t>
+          <t>3,84; 13,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 7,12</t>
+          <t>-3,87; 6,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 6,6</t>
+          <t>-3,79; 6,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,14</t>
+          <t>3,53; 13,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 7,55</t>
+          <t>0,37; 7,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,31</t>
+          <t>-1,5; 5,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,88</t>
+          <t>5,11; 11,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,9; 157,93</t>
+          <t>6,81; 165,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 97,72</t>
+          <t>-21,41; 99,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,89; 202,76</t>
+          <t>31,14; 193,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 70,95</t>
+          <t>-26,44; 67,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 65,7</t>
+          <t>-25,43; 66,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 133,34</t>
+          <t>22,22; 132,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 79,61</t>
+          <t>2,59; 77,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 59,96</t>
+          <t>-11,99; 54,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,66; 129,25</t>
+          <t>39,98; 132,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,65</t>
+          <t>1,31; 10,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 7,5</t>
+          <t>-2,03; 7,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,08; 68,23</t>
+          <t>7,55; 67,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 11,61</t>
+          <t>-8,35; 10,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 13,06</t>
+          <t>-6,74; 13,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 21,73</t>
+          <t>4,11; 21,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,33</t>
+          <t>0,94; 9,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,99</t>
+          <t>-1,67; 6,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 59,84</t>
+          <t>9,52; 59,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 76,84</t>
+          <t>6,78; 76,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 55,34</t>
+          <t>-11,56; 51,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50,54; 498,48</t>
+          <t>45,34; 507,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 51,1</t>
+          <t>-25,45; 45,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 58,09</t>
+          <t>-21,28; 63,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 98,46</t>
+          <t>11,62; 98,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 57,57</t>
+          <t>3,39; 56,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 42,43</t>
+          <t>-7,82; 42,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,91; 366,01</t>
+          <t>47,82; 339,98</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,62</t>
+          <t>-3,16; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,59</t>
+          <t>-5,07; 1,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,82</t>
+          <t>-6,44; 2,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,92</t>
+          <t>-7,76; 0,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 5,42</t>
+          <t>-12,95; 5,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,72</t>
+          <t>-3,94; 1,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,2</t>
+          <t>-4,79; 0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 6,02</t>
+          <t>-5,86; 6,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 19,1</t>
+          <t>-14,2; 19,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 8,42</t>
+          <t>-22,57; 8,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,88; 47,48</t>
+          <t>8,53; 47,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 8,91</t>
+          <t>-25,64; 10,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 4,66</t>
+          <t>-30,95; 3,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 24,79</t>
+          <t>-54,5; 22,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 8,28</t>
+          <t>-16,93; 7,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 1,02</t>
+          <t>-20,58; 1,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 28,38</t>
+          <t>-25,88; 28,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,76</t>
+          <t>-5,92; 4,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 7,8</t>
+          <t>-3,49; 7,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,96</t>
+          <t>2,52; 14,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,79</t>
+          <t>4,37; 15,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 9,68</t>
+          <t>-0,67; 9,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 13,0</t>
+          <t>-2,57; 13,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,73</t>
+          <t>1,75; 9,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,25</t>
+          <t>-0,54; 7,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,15</t>
+          <t>1,58; 12,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 34,89</t>
+          <t>-25,45; 26,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 45,92</t>
+          <t>-14,55; 45,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,2; 90,27</t>
+          <t>11,18; 85,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,05; 61,6</t>
+          <t>14,59; 60,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 37,92</t>
+          <t>-2,07; 38,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 49,15</t>
+          <t>-6,05; 54,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,31; 42,92</t>
+          <t>6,48; 43,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 32,47</t>
+          <t>-1,97; 31,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,46; 52,16</t>
+          <t>6,77; 54,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,17</t>
+          <t>-2,23; 4,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,58</t>
+          <t>-4,15; 1,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,38</t>
+          <t>-3,07; 3,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 5,57</t>
+          <t>-2,37; 5,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,06</t>
+          <t>-6,22; 2,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 4,44</t>
+          <t>-3,56; 4,69</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,87</t>
+          <t>-2,42; 4,83</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,83</t>
+          <t>-6,13; 0,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,3</t>
+          <t>-4,72; 2,36</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 168,28</t>
+          <t>-45,68; 208,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,44; 72,15</t>
+          <t>-80,52; 73,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-57,02; 173,48</t>
+          <t>-59,1; 163,95</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 16,19</t>
+          <t>-6,38; 16,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 6,17</t>
+          <t>-16,88; 6,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 13,44</t>
+          <t>-9,49; 13,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 17,57</t>
+          <t>-7,77; 17,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 2,78</t>
+          <t>-19,51; 2,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 8,27</t>
+          <t>-15,41; 8,42</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,99</t>
+          <t>0,28; 3,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,76</t>
+          <t>-0,91; 2,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,18; 28,87</t>
+          <t>5,15; 29,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,08</t>
+          <t>-0,3; 4,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,03</t>
+          <t>-3,3; 1,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,91</t>
+          <t>-4,42; 4,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,43</t>
+          <t>0,55; 3,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,32</t>
+          <t>-1,54; 1,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,97; 15,07</t>
+          <t>2,6; 14,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,34; 26,45</t>
+          <t>1,55; 25,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 18,47</t>
+          <t>-5,83; 17,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32,11; 190,46</t>
+          <t>32,36; 189,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 15,66</t>
+          <t>-1,05; 15,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 3,95</t>
+          <t>-11,76; 3,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 14,79</t>
+          <t>-16,41; 15,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,6</t>
+          <t>2,42; 16,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 6,24</t>
+          <t>-6,94; 5,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,4; 69,82</t>
+          <t>11,87; 68,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 5,66</t>
+          <t>-3,67; 5,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,18</t>
+          <t>-2,81; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,83</t>
+          <t>-2,23; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 2,95</t>
+          <t>-8,86; 3,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,73</t>
+          <t>-8,64; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,79</t>
+          <t>-3,46; 7,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 3,22</t>
+          <t>-3,85; 3,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,82</t>
+          <t>-3,8; 3,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,5</t>
+          <t>-0,9; 5,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 57,51</t>
+          <t>-26,8; 56,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 62,67</t>
+          <t>-20,11; 65,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 59,96</t>
+          <t>-16,69; 64,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 22,22</t>
+          <t>-42,82; 23,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 24,47</t>
+          <t>-40,53; 26,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 46,02</t>
+          <t>-16,63; 54,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 25,95</t>
+          <t>-24,0; 27,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 29,23</t>
+          <t>-23,72; 27,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 45,79</t>
+          <t>-5,33; 43,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,23</t>
+          <t>1,29; 11,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,77</t>
+          <t>-2,33; 6,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,38</t>
+          <t>3,46; 12,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 6,98</t>
+          <t>-3,57; 6,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,62</t>
+          <t>-4,2; 6,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,52</t>
+          <t>4,68; 13,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 7,27</t>
+          <t>0,62; 7,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,21</t>
+          <t>-1,62; 5,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,86</t>
+          <t>5,15; 11,47</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 165,47</t>
+          <t>9,91; 162,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 99,0</t>
+          <t>-21,88; 107,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,14; 193,89</t>
+          <t>29,49; 182,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 67,04</t>
+          <t>-23,21; 66,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 66,61</t>
+          <t>-27,73; 62,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 132,87</t>
+          <t>28,37; 134,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 77,5</t>
+          <t>4,34; 86,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 54,68</t>
+          <t>-12,95; 58,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,98; 132,59</t>
+          <t>38,96; 122,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36,62</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>11,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>10,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,67</t>
+          <t>0,98; 10,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,12</t>
+          <t>-1,79; 7,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 67,17</t>
+          <t>3,73; 13,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 10,32</t>
+          <t>-7,41; 10,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 13,87</t>
+          <t>-8,05; 12,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 21,16</t>
+          <t>2,37; 20,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,61</t>
+          <t>0,68; 9,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,97</t>
+          <t>-1,58; 7,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 59,3</t>
+          <t>5,83; 14,67</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228,41%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>168,38%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 76,72</t>
+          <t>5,37; 75,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 51,35</t>
+          <t>-10,48; 50,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,34; 507,2</t>
+          <t>19,8; 98,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 45,98</t>
+          <t>-23,09; 48,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 63,32</t>
+          <t>-26,38; 54,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,62; 98,22</t>
+          <t>7,06; 93,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 56,29</t>
+          <t>2,63; 56,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 42,17</t>
+          <t>-8,15; 42,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,82; 339,98</t>
+          <t>26,73; 87,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,81</t>
+          <t>-3,51; 3,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,65</t>
+          <t>-4,67; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,35</t>
+          <t>1,93; 8,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,12</t>
+          <t>-6,25; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,7</t>
+          <t>-7,31; 0,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 5,03</t>
+          <t>-0,29; 7,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,51</t>
+          <t>-3,48; 1,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,16</t>
+          <t>-4,84; 0,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,08</t>
+          <t>2,22; 7,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-8,02%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 19,54</t>
+          <t>-15,99; 15,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 8,8</t>
+          <t>-21,69; 8,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 47,93</t>
+          <t>8,44; 44,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 10,5</t>
+          <t>-25,45; 9,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 3,46</t>
+          <t>-30,06; 3,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 22,82</t>
+          <t>-1,31; 38,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 7,52</t>
+          <t>-15,23; 9,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 1,07</t>
+          <t>-21,14; 1,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 28,66</t>
+          <t>9,92; 35,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>10,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>8,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 4,53</t>
+          <t>-6,39; 5,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 7,53</t>
+          <t>-2,75; 7,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,35</t>
+          <t>0,51; 11,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 15,11</t>
+          <t>4,15; 14,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 9,85</t>
+          <t>-1,1; 9,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 13,69</t>
+          <t>5,61; 15,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,62</t>
+          <t>1,74; 9,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 7,2</t>
+          <t>-0,79; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,33</t>
+          <t>4,85; 12,35</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 26,42</t>
+          <t>-27,4; 31,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 45,99</t>
+          <t>-12,0; 44,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11,18; 85,31</t>
+          <t>2,1; 71,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,59; 60,5</t>
+          <t>13,72; 59,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 38,86</t>
+          <t>-3,64; 35,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 54,46</t>
+          <t>18,04; 59,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,48; 43,36</t>
+          <t>6,23; 42,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 31,74</t>
+          <t>-3,09; 31,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,77; 54,32</t>
+          <t>17,18; 53,81</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,95</t>
+          <t>-2,58; 4,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,46</t>
+          <t>-4,25; 1,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,57</t>
+          <t>-2,66; 4,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,68</t>
+          <t>-2,33; 5,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 2,2</t>
+          <t>-6,2; 1,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,69</t>
+          <t>-4,6; 3,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,83</t>
+          <t>-2,12; 4,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,77</t>
+          <t>-6,02; 0,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,36</t>
+          <t>-4,69; 2,1</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-3,16%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>-1,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
+          <t>-4,02%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 208,12</t>
+          <t>-51,07; 191,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 73,39</t>
+          <t>-79,39; 82,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 163,95</t>
+          <t>-53,65; 194,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 16,99</t>
+          <t>-6,2; 17,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 6,35</t>
+          <t>-16,64; 4,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 13,65</t>
+          <t>-12,1; 11,57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 17,43</t>
+          <t>-6,84; 16,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 2,76</t>
+          <t>-19,81; 2,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 8,42</t>
+          <t>-14,86; 7,6</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,45</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>4,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,89</t>
+          <t>0,29; 3,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,62</t>
+          <t>-0,99; 2,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,15; 29,71</t>
+          <t>3,41; 7,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,05</t>
+          <t>-0,38; 3,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,01</t>
+          <t>-3,41; 0,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,06</t>
+          <t>1,51; 5,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,41</t>
+          <t>0,62; 3,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,24</t>
+          <t>-1,47; 1,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,6; 14,77</t>
+          <t>3,1; 5,84</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,55; 25,94</t>
+          <t>1,57; 25,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 17,29</t>
+          <t>-5,74; 18,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32,36; 189,43</t>
+          <t>20,83; 48,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 15,48</t>
+          <t>-1,35; 15,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 3,77</t>
+          <t>-11,96; 3,55</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 15,15</t>
+          <t>5,39; 20,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,42; 16,36</t>
+          <t>2,74; 16,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,96</t>
+          <t>-6,64; 6,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,87; 68,69</t>
+          <t>13,9; 28,16</t>
         </is>
       </c>
     </row>
